--- a/docentes/Medina Tolentino Elio - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20222.xlsx
@@ -678,16 +678,19 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>31</v>
       </c>
-      <c r="E2">
-        <v>31</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -701,16 +704,19 @@
         <v>27</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>27</v>
       </c>
-      <c r="E3">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -724,16 +730,19 @@
         <v>41</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>41</v>
       </c>
-      <c r="E4">
-        <v>41</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -747,16 +756,19 @@
         <v>30</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>30</v>
       </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -770,16 +782,19 @@
         <v>20</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>20</v>
       </c>
-      <c r="E6">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -793,16 +808,19 @@
         <v>28</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>28</v>
       </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -867,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -893,7 +911,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -945,7 +963,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -971,7 +989,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -997,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,42 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARCOS SURIEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>AMIR ALONSO</t>
   </si>
 </sst>
 </file>
@@ -876,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>92.59</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -928,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -954,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H5">
         <v>7.4</v>
@@ -980,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1006,16 +1042,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1055,6 +1091,98 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920035</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920340</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920154</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920351</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -85,37 +85,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>XOCUA</t>
   </si>
   <si>
     <t>CUEVAS</t>
   </si>
   <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
     <t>BAROJAS</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>MONGE</t>
   </si>
   <si>
+    <t>NERI</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
     <t>MARCOS SURIEL</t>
   </si>
   <si>
     <t>CESAR</t>
   </si>
   <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
     <t>MARIEL</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>AMIR ALONSO</t>
@@ -1061,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1093,22 +1120,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920035</v>
+        <v>21330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1116,22 +1143,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920340</v>
+        <v>20330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1139,47 +1166,116 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920154</v>
+        <v>20330051920340</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920351</v>
+        <v>20330051920042</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920154</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920351</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G8">
         <v>1</v>
       </c>
     </row>
